--- a/output/topology_excel/8073.xlsx
+++ b/output/topology_excel/8073.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -792,10 +792,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>9</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -836,10 +836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -847,21 +847,21 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>302</v>
+        <v>183</v>
       </c>
       <c r="F19" t="n">
-        <v>126</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="F20" t="n">
         <v>33</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
@@ -902,24 +902,24 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Window</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>310</v>
+        <v>118</v>
       </c>
       <c r="F22" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
@@ -927,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>652</v>
+        <v>35</v>
       </c>
       <c r="F23" t="n">
-        <v>92</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="F25" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,19 +1004,19 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="n">
         <v>3</v>
       </c>
-      <c r="B27" t="n">
-        <v>5</v>
-      </c>
       <c r="C27" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>374</v>
       </c>
       <c r="F27" t="n">
         <v>14</v>
@@ -1034,10 +1034,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>126</v>
+        <v>278</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="F29" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F30" t="n">
         <v>14</v>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B32" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,40 +1136,40 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>186</v>
+        <v>245</v>
       </c>
       <c r="F32" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B33" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>147</v>
+      </c>
+      <c r="F33" t="n">
         <v>8</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>313</v>
-      </c>
-      <c r="F33" t="n">
-        <v>111</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,18 +1180,18 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>191</v>
+        <v>163</v>
       </c>
       <c r="F34" t="n">
-        <v>135</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,15 +1202,15 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>413</v>
+        <v>154</v>
       </c>
       <c r="F35" t="n">
-        <v>197</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B36" t="n">
         <v>12</v>
@@ -1224,18 +1224,18 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>397</v>
+        <v>310</v>
       </c>
       <c r="F36" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="F37" t="n">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,18 +1268,18 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>117</v>
+        <v>206</v>
       </c>
       <c r="F38" t="n">
-        <v>112</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>200</v>
+        <v>310</v>
       </c>
       <c r="F39" t="n">
         <v>13</v>
@@ -1298,10 +1298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,19 +1312,19 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="F40" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" t="n">
         <v>10</v>
       </c>
-      <c r="B41" t="n">
-        <v>12</v>
-      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1334,18 +1334,18 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>322</v>
+        <v>211</v>
       </c>
       <c r="F41" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1356,18 +1356,18 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="F42" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,18 +1378,18 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="F43" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1400,18 +1400,18 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>161</v>
+        <v>200</v>
       </c>
       <c r="F44" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,18 +1422,18 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F45" t="n">
-        <v>14</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1444,18 +1444,18 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>161</v>
+        <v>319</v>
       </c>
       <c r="F46" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1466,18 +1466,18 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>319</v>
+        <v>169</v>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B48" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1510,18 +1510,18 @@
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>27</v>
+        <v>174</v>
       </c>
       <c r="F49" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1532,18 +1532,18 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="F50" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1554,15 +1554,15 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>308</v>
+        <v>177</v>
       </c>
       <c r="F51" t="n">
-        <v>31</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B52" t="n">
         <v>16</v>
@@ -1576,18 +1576,18 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>214</v>
+        <v>144</v>
       </c>
       <c r="F52" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B53" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1602,6 +1602,402 @@
       </c>
       <c r="F53" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" t="n">
+        <v>13</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>100</v>
+      </c>
+      <c r="F54" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" t="n">
+        <v>14</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>126</v>
+      </c>
+      <c r="F55" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>13</v>
+      </c>
+      <c r="B56" t="n">
+        <v>14</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>125</v>
+      </c>
+      <c r="F56" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>13</v>
+      </c>
+      <c r="B57" t="n">
+        <v>15</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>99</v>
+      </c>
+      <c r="F57" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>13</v>
+      </c>
+      <c r="B58" t="n">
+        <v>16</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>177</v>
+      </c>
+      <c r="F58" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>13</v>
+      </c>
+      <c r="B59" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>295</v>
+      </c>
+      <c r="F59" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>16</v>
+      </c>
+      <c r="B60" t="n">
+        <v>18</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>322</v>
+      </c>
+      <c r="F60" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>17</v>
+      </c>
+      <c r="B61" t="n">
+        <v>18</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>161</v>
+      </c>
+      <c r="F61" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>17</v>
+      </c>
+      <c r="B62" t="n">
+        <v>19</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>161</v>
+      </c>
+      <c r="F62" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>17</v>
+      </c>
+      <c r="B63" t="n">
+        <v>20</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>174</v>
+      </c>
+      <c r="F63" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>18</v>
+      </c>
+      <c r="B64" t="n">
+        <v>19</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>161</v>
+      </c>
+      <c r="F64" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>19</v>
+      </c>
+      <c r="B65" t="n">
+        <v>20</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>27</v>
+      </c>
+      <c r="F65" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20</v>
+      </c>
+      <c r="B66" t="n">
+        <v>21</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>214</v>
+      </c>
+      <c r="F66" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" t="n">
+        <v>10</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>68</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" t="n">
+        <v>10</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>77</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2</v>
+      </c>
+      <c r="B69" t="n">
+        <v>13</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>161</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" t="n">
+        <v>13</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>146</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="n">
+        <v>13</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>133</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/8073.xlsx
+++ b/output/topology_excel/8073.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>13</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>14</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>14</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>8</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>53</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>13</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -627,7 +651,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>139</v>
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>19</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>20</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>11</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>14</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>22</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>14</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>14</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +827,8 @@
       <c r="F16" t="n">
         <v>11</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>12</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>20</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -847,7 +891,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>183</v>
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>93</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>33</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>33</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +971,8 @@
       <c r="F22" t="n">
         <v>33</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +995,8 @@
       <c r="F23" t="n">
         <v>12</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1019,8 @@
       <c r="F24" t="n">
         <v>12</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1043,8 @@
       <c r="F25" t="n">
         <v>43</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1067,8 @@
       <c r="F26" t="n">
         <v>11</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1091,8 @@
       <c r="F27" t="n">
         <v>14</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1051,8 +1113,10 @@
         <v>278</v>
       </c>
       <c r="F28" t="n">
-        <v>92</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1073,8 +1137,10 @@
         <v>98</v>
       </c>
       <c r="F29" t="n">
-        <v>75</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1089,12 +1155,18 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>309</v>
+        <v>61</v>
       </c>
       <c r="F30" t="n">
+        <v>13</v>
+      </c>
+      <c r="G30" t="n">
+        <v>87</v>
+      </c>
+      <c r="H30" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1119,6 +1191,8 @@
       <c r="F31" t="n">
         <v>14</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1139,8 +1213,10 @@
         <v>245</v>
       </c>
       <c r="F32" t="n">
-        <v>91</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1163,6 +1239,8 @@
       <c r="F33" t="n">
         <v>8</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1177,13 +1255,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="F34" t="n">
-        <v>59</v>
+        <v>8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>78</v>
+      </c>
+      <c r="H34" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1205,8 +1289,10 @@
         <v>154</v>
       </c>
       <c r="F35" t="n">
-        <v>91</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1229,6 +1315,8 @@
       <c r="F36" t="n">
         <v>11</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1249,8 +1337,10 @@
         <v>156</v>
       </c>
       <c r="F37" t="n">
-        <v>91</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1271,8 +1361,10 @@
         <v>206</v>
       </c>
       <c r="F38" t="n">
-        <v>75</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1387,8 @@
       <c r="F39" t="n">
         <v>13</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1411,8 @@
       <c r="F40" t="n">
         <v>14</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1331,13 +1427,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
-        <v>211</v>
+        <v>78</v>
       </c>
       <c r="F41" t="n">
         <v>15</v>
+      </c>
+      <c r="G41" t="n">
+        <v>65</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1359,8 +1461,10 @@
         <v>67</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1381,8 +1485,10 @@
         <v>117</v>
       </c>
       <c r="F43" t="n">
-        <v>112</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1511,8 @@
       <c r="F44" t="n">
         <v>13</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1425,8 +1533,10 @@
         <v>186</v>
       </c>
       <c r="F45" t="n">
-        <v>103</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1449,6 +1559,8 @@
       <c r="F46" t="n">
         <v>14</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1471,6 +1583,8 @@
       <c r="F47" t="n">
         <v>33</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1493,6 +1607,8 @@
       <c r="F48" t="n">
         <v>14</v>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1515,6 +1631,8 @@
       <c r="F49" t="n">
         <v>11</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1537,6 +1655,8 @@
       <c r="F50" t="n">
         <v>31</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1551,13 +1671,19 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="F51" t="n">
-        <v>135</v>
+        <v>12</v>
+      </c>
+      <c r="G51" t="n">
+        <v>123</v>
+      </c>
+      <c r="H51" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -1579,8 +1705,10 @@
         <v>144</v>
       </c>
       <c r="F52" t="n">
-        <v>32</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1603,6 +1731,8 @@
       <c r="F53" t="n">
         <v>12</v>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1625,6 +1755,8 @@
       <c r="F54" t="n">
         <v>14</v>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1647,6 +1779,8 @@
       <c r="F55" t="n">
         <v>14</v>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1667,8 +1801,10 @@
         <v>125</v>
       </c>
       <c r="F56" t="n">
-        <v>33</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1691,6 +1827,8 @@
       <c r="F57" t="n">
         <v>13</v>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1713,6 +1851,8 @@
       <c r="F58" t="n">
         <v>33</v>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1735,6 +1875,8 @@
       <c r="F59" t="n">
         <v>14</v>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1755,8 +1897,10 @@
         <v>322</v>
       </c>
       <c r="F60" t="n">
-        <v>33</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1777,8 +1921,10 @@
         <v>161</v>
       </c>
       <c r="F61" t="n">
-        <v>81</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1793,13 +1939,19 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="F62" t="n">
-        <v>56</v>
+        <v>14</v>
+      </c>
+      <c r="G62" t="n">
+        <v>147</v>
+      </c>
+      <c r="H62" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="63">
@@ -1823,6 +1975,8 @@
       <c r="F63" t="n">
         <v>14</v>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1837,13 +1991,19 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
-        <v>161</v>
+        <v>67</v>
       </c>
       <c r="F64" t="n">
-        <v>78</v>
+        <v>14</v>
+      </c>
+      <c r="G64" t="n">
+        <v>147</v>
+      </c>
+      <c r="H64" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -1867,6 +2027,8 @@
       <c r="F65" t="n">
         <v>14</v>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1889,6 +2051,8 @@
       <c r="F66" t="n">
         <v>31</v>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1911,6 +2075,8 @@
       <c r="F67" t="n">
         <v>1</v>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1933,6 +2099,8 @@
       <c r="F68" t="n">
         <v>1</v>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1955,6 +2123,8 @@
       <c r="F69" t="n">
         <v>1</v>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1969,7 +2139,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
         <v>146</v>
@@ -1977,26 +2147,10 @@
       <c r="F70" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>1</v>
-      </c>
-      <c r="B71" t="n">
-        <v>13</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="G70" t="n">
         <v>133</v>
       </c>
-      <c r="F71" t="n">
+      <c r="H70" t="n">
         <v>1</v>
       </c>
     </row>
